--- a/Nhom8_HeThongPhongKham_Ver02.xlsx
+++ b/Nhom8_HeThongPhongKham_Ver02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2.CNPMNangCao\LyThuyet\Tuan04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638772F5-CE95-4125-85E8-E55EC381D727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1766746C-E740-4530-A051-14EF5343604A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="798" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Information" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="136">
   <si>
     <t>I. Requirements</t>
   </si>
@@ -426,6 +426,24 @@
   </si>
   <si>
     <t>Tra cứu thông tin đặt lịch khám của khách hàng</t>
+  </si>
+  <si>
+    <t>17/9/2025</t>
+  </si>
+  <si>
+    <t>30/9/2025</t>
+  </si>
+  <si>
+    <t>26/9/2025</t>
+  </si>
+  <si>
+    <t>27/9/2025</t>
+  </si>
+  <si>
+    <t>28/9/2025</t>
+  </si>
+  <si>
+    <t>29/9/2025</t>
   </si>
 </sst>
 </file>
@@ -489,7 +507,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,6 +556,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="24">
     <border>
@@ -811,7 +835,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -997,7 +1021,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -2367,7 +2393,9 @@
       <c r="D4" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="44"/>
+      <c r="E4" s="44" t="s">
+        <v>130</v>
+      </c>
       <c r="F4" s="41"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2484,7 +2512,7 @@
       <c r="C6" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="78">
         <v>2</v>
       </c>
     </row>
@@ -2493,10 +2521,10 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="77" t="s">
+      <c r="C7" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="77">
         <v>2</v>
       </c>
       <c r="H7" s="11"/>
@@ -2509,7 +2537,7 @@
       <c r="C8" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="77">
         <v>2</v>
       </c>
       <c r="H8" s="11"/>
@@ -2522,7 +2550,7 @@
       <c r="C9" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="77">
         <v>2</v>
       </c>
       <c r="H9" s="11"/>
@@ -2587,7 +2615,7 @@
       <c r="C14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="77">
         <v>2</v>
       </c>
     </row>
@@ -2599,7 +2627,7 @@
       <c r="C15" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="77">
         <v>4</v>
       </c>
     </row>
@@ -2611,7 +2639,7 @@
       <c r="C16" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="77">
         <v>2</v>
       </c>
     </row>
@@ -3095,7 +3123,7 @@
       <c r="F6" s="73"/>
       <c r="G6" s="73"/>
       <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
+      <c r="I6" s="74"/>
       <c r="J6" s="73"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -3111,18 +3139,28 @@
       <c r="D7" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="E7" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H7" s="79" t="s">
+        <v>132</v>
+      </c>
+      <c r="I7" s="4">
+        <v>2</v>
+      </c>
+      <c r="J7" s="48"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="31">
         <v>2</v>
       </c>
-      <c r="B8" s="77" t="s">
+      <c r="B8" t="s">
         <v>124</v>
       </c>
       <c r="C8" s="33">
@@ -3131,12 +3169,22 @@
       <c r="D8" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="E8" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H8" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="I8" s="4">
+        <v>2</v>
+      </c>
+      <c r="J8" s="48"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="31">
@@ -3151,12 +3199,22 @@
       <c r="D9" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="E9" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H9" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="4">
+        <v>2</v>
+      </c>
+      <c r="J9" s="48"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="31">
@@ -3171,12 +3229,22 @@
       <c r="D10" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="E10" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H10" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="I10" s="4">
+        <v>4</v>
+      </c>
+      <c r="J10" s="48"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="31">
@@ -3191,12 +3259,22 @@
       <c r="D11" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+      <c r="E11" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H11" s="79" t="s">
+        <v>131</v>
+      </c>
+      <c r="I11" s="4">
+        <v>2</v>
+      </c>
+      <c r="J11" s="48"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="31">
@@ -3211,12 +3289,22 @@
       <c r="D12" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
+      <c r="E12" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="H12" s="79" t="s">
+        <v>134</v>
+      </c>
+      <c r="I12" s="4">
+        <v>2</v>
+      </c>
+      <c r="J12" s="48"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="31">
@@ -3231,12 +3319,22 @@
       <c r="D13" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+      <c r="E13" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="H13" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="I13" s="4">
+        <v>2</v>
+      </c>
+      <c r="J13" s="48"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="72"/>
